--- a/data/trans_orig/P0801-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2007</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>415226</t>
+          <t>415208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>441681</t>
+          <t>441572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248490</t>
+          <t>247563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>272750</t>
+          <t>272367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>673160</t>
+          <t>672459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>708948</t>
+          <t>707924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19422</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39246</t>
+          <t>39113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>46081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47935</t>
+          <t>47580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77882</t>
+          <t>76788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>26899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40536</t>
+          <t>40432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>335019</t>
+          <t>336557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354582</t>
+          <t>355459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339539</t>
+          <t>339248</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358388</t>
+          <t>358096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683372</t>
+          <t>683152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>708293</t>
+          <t>708214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25079</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>18527</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40515</t>
+          <t>40072</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>463681</t>
+          <t>464158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>493436</t>
+          <t>493283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115248</t>
+          <t>115830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137715</t>
+          <t>137448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>587910</t>
+          <t>585505</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>625269</t>
+          <t>624002</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35482</t>
+          <t>34826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60980</t>
+          <t>60683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40163</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60276</t>
+          <t>60688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91859</t>
+          <t>93561</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>39134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1033507</t>
+          <t>1031359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1081184</t>
+          <t>1079190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>560695</t>
+          <t>558533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>601058</t>
+          <t>601272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1606700</t>
+          <t>1608063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1670088</t>
+          <t>1670412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112936</t>
+          <t>113197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157249</t>
+          <t>156501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90708</t>
+          <t>90218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128897</t>
+          <t>129505</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213857</t>
+          <t>214133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272514</t>
+          <t>270967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36590</t>
+          <t>36256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63367</t>
+          <t>64145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34551</t>
+          <t>35460</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57084</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>92205</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286754</t>
+          <t>287826</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312600</t>
+          <t>312980</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>436367</t>
+          <t>436687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>473637</t>
+          <t>473954</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>732157</t>
+          <t>733011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>779096</t>
+          <t>778539</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26861</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49730</t>
+          <t>48951</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65794</t>
+          <t>65047</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99820</t>
+          <t>99525</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98835</t>
+          <t>98694</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140196</t>
+          <t>138926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46968</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33680</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61235</t>
+          <t>60497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>283648</t>
+          <t>283642</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>294524</t>
+          <t>294573</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>842775</t>
+          <t>845228</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>909256</t>
+          <t>911194</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1138119</t>
+          <t>1135389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1206315</t>
+          <t>1200675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,62%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>245894</t>
+          <t>245030</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>304507</t>
+          <t>301359</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>247342</t>
+          <t>249179</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>306210</t>
+          <t>308573</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78763</t>
+          <t>77267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119139</t>
+          <t>116352</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79681</t>
+          <t>79583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120422</t>
+          <t>117823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2866358</t>
+          <t>2867022</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2936709</t>
+          <t>2939619</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2603794</t>
+          <t>2605982</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2699859</t>
+          <t>2703442</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5500603</t>
+          <t>5495115</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5617796</t>
+          <t>5612627</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>234754</t>
+          <t>236065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>296465</t>
+          <t>298654</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>499964</t>
+          <t>499510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>584867</t>
+          <t>585959</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>750078</t>
+          <t>755447</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>858089</t>
+          <t>862237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83477</t>
+          <t>82784</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>124325</t>
+          <t>121848</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>158091</t>
+          <t>156687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>213395</t>
+          <t>211582</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>252088</t>
+          <t>253517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>317942</t>
+          <t>320932</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2012</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371578</t>
+          <t>373026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>401875</t>
+          <t>401011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>264092</t>
+          <t>262750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287917</t>
+          <t>288270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>645567</t>
+          <t>646284</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>683765</t>
+          <t>683479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57197</t>
+          <t>55909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>54852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90047</t>
+          <t>89065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>16414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>352812</t>
+          <t>350007</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381306</t>
+          <t>380315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>287852</t>
+          <t>288345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312256</t>
+          <t>312879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649580</t>
+          <t>648436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>686849</t>
+          <t>687469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26388</t>
+          <t>26273</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37196</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47855</t>
+          <t>47559</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79386</t>
+          <t>80327</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>21015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39343</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>501635</t>
+          <t>502496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>542534</t>
+          <t>542006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179621</t>
+          <t>178850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209220</t>
+          <t>208262</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>692530</t>
+          <t>691856</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>742834</t>
+          <t>740986</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55061</t>
+          <t>55086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87766</t>
+          <t>88227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>51803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>88529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130142</t>
+          <t>130085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25504</t>
+          <t>25390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51947</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>38916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81556</t>
+          <t>80236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>932714</t>
+          <t>933790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>987045</t>
+          <t>986956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>621901</t>
+          <t>624931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>664184</t>
+          <t>665582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1572943</t>
+          <t>1573025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1641332</t>
+          <t>1639270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103306</t>
+          <t>102226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146751</t>
+          <t>147444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64766</t>
+          <t>64728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99465</t>
+          <t>100642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176790</t>
+          <t>178226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234133</t>
+          <t>232154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58188</t>
+          <t>58430</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93439</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93291</t>
+          <t>94859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137343</t>
+          <t>137883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>405029</t>
+          <t>402966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>439028</t>
+          <t>437379</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>478649</t>
+          <t>478082</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>533775</t>
+          <t>531143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>896992</t>
+          <t>894477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>960782</t>
+          <t>958061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44809</t>
+          <t>45549</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74803</t>
+          <t>74689</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135946</t>
+          <t>135390</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182792</t>
+          <t>184074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>189572</t>
+          <t>191139</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>243139</t>
+          <t>244821</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>19930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80341</t>
+          <t>79968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117146</t>
+          <t>117429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105722</t>
+          <t>104521</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>151296</t>
+          <t>146980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>248651</t>
+          <t>248182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>262024</t>
+          <t>261969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>694266</t>
+          <t>695785</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>758991</t>
+          <t>760573</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>948521</t>
+          <t>949666</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1016734</t>
+          <t>1019039</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>217089</t>
+          <t>216889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>272382</t>
+          <t>273426</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>222929</t>
+          <t>221468</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282262</t>
+          <t>278971</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114759</t>
+          <t>114566</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159551</t>
+          <t>162091</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>119707</t>
+          <t>119434</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>165792</t>
+          <t>165593</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2877464</t>
+          <t>2874003</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2969155</t>
+          <t>2963717</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2598443</t>
+          <t>2596738</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2706054</t>
+          <t>2703985</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5501242</t>
+          <t>5500427</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5646124</t>
+          <t>5635453</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>295749</t>
+          <t>298127</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>373117</t>
+          <t>373716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>533426</t>
+          <t>533256</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>623772</t>
+          <t>623652</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>853600</t>
+          <t>859238</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>975654</t>
+          <t>971515</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>140811</t>
+          <t>138505</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>195626</t>
+          <t>195358</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>283758</t>
+          <t>288322</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>353934</t>
+          <t>356813</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>442229</t>
+          <t>445581</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>533552</t>
+          <t>532866</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2016</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371841</t>
+          <t>372798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396659</t>
+          <t>396854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>291171</t>
+          <t>292225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>317954</t>
+          <t>317961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>673448</t>
+          <t>671823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>708344</t>
+          <t>708762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41581</t>
+          <t>42957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36125</t>
+          <t>35231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>41007</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69899</t>
+          <t>72599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>22098</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>27397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>43219</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>326115</t>
+          <t>325984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>350661</t>
+          <t>350727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318642</t>
+          <t>319953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344443</t>
+          <t>345481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>654664</t>
+          <t>655227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689514</t>
+          <t>690173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>15550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36021</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36828</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66504</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20412</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22787</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>36131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>429037</t>
+          <t>429644</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>458900</t>
+          <t>461603</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113584</t>
+          <t>112551</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>136925</t>
+          <t>137641</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>550284</t>
+          <t>550137</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>589849</t>
+          <t>591142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38666</t>
+          <t>39604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63383</t>
+          <t>65059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>15892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>38170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60697</t>
+          <t>59493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95189</t>
+          <t>93489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>38835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29962</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>54613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>942709</t>
+          <t>939811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>991448</t>
+          <t>992074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>665536</t>
+          <t>664980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>708451</t>
+          <t>709573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1625568</t>
+          <t>1623191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1688465</t>
+          <t>1690932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105351</t>
+          <t>103322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147911</t>
+          <t>146902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65099</t>
+          <t>66019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100776</t>
+          <t>100698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179352</t>
+          <t>178672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233039</t>
+          <t>234305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42529</t>
+          <t>43008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73651</t>
+          <t>72370</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41800</t>
+          <t>40703</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>71299</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>90861</t>
+          <t>93177</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134535</t>
+          <t>136458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>474716</t>
+          <t>474888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>514126</t>
+          <t>513569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>500426</t>
+          <t>498778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>548846</t>
+          <t>552311</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>989058</t>
+          <t>985493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1053261</t>
+          <t>1050749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73378</t>
+          <t>73800</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>109376</t>
+          <t>108678</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>118149</t>
+          <t>115526</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>158416</t>
+          <t>160803</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>200008</t>
+          <t>203059</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>256293</t>
+          <t>258494</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26058</t>
+          <t>24077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48303</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59419</t>
+          <t>57727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94173</t>
+          <t>91680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90796</t>
+          <t>90169</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130636</t>
+          <t>131512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274289</t>
+          <t>273432</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285008</t>
+          <t>284939</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>720591</t>
+          <t>720451</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>786714</t>
+          <t>788184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1000964</t>
+          <t>1003622</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1069066</t>
+          <t>1067962</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176589</t>
+          <t>179106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>231099</t>
+          <t>231329</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180225</t>
+          <t>180668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>234704</t>
+          <t>236406</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100516</t>
+          <t>101271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148216</t>
+          <t>146982</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>102792</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149931</t>
+          <t>150354</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2873944</t>
+          <t>2875965</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2955956</t>
+          <t>2956704</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2681668</t>
+          <t>2680991</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2784552</t>
+          <t>2784292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5582858</t>
+          <t>5587370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5717373</t>
+          <t>5716807</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>289206</t>
+          <t>288433</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>364003</t>
+          <t>357201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>456703</t>
+          <t>452566</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>540263</t>
+          <t>542848</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>768124</t>
+          <t>767267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>882377</t>
+          <t>878087</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124581</t>
+          <t>124154</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>172098</t>
+          <t>170794</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>263612</t>
+          <t>265470</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>334111</t>
+          <t>339286</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>402101</t>
+          <t>402373</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>491207</t>
+          <t>490282</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2023</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>455773</t>
+          <t>455050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>477738</t>
+          <t>477503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>381631</t>
+          <t>382518</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>403601</t>
+          <t>404816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>846681</t>
+          <t>846240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>878058</t>
+          <t>876877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31889</t>
+          <t>33439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30224</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49425</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49760</t>
+          <t>49602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74780</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22152</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37946</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384532</t>
+          <t>384320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413020</t>
+          <t>410851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316934</t>
+          <t>315447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338074</t>
+          <t>337778</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708892</t>
+          <t>708618</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743197</t>
+          <t>743160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29823</t>
+          <t>31331</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>57055</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30401</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47854</t>
+          <t>49352</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>65632</t>
+          <t>65656</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>97570</t>
+          <t>96675</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>23479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37551</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122047</t>
+          <t>138935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>558648</t>
+          <t>562832</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111430</t>
+          <t>111481</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129254</t>
+          <t>129436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>197665</t>
+          <t>218092</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>676799</t>
+          <t>675972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79423</t>
+          <t>77451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>535815</t>
+          <t>520218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110508</t>
+          <t>110501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>620662</t>
+          <t>600364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33623</t>
+          <t>35029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53817</t>
+          <t>54007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>817507</t>
+          <t>819811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>866806</t>
+          <t>868782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>815502</t>
+          <t>815638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>918394</t>
+          <t>908470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1648012</t>
+          <t>1651780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1784022</t>
+          <t>1798414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114024</t>
+          <t>115350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157024</t>
+          <t>158101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109614</t>
+          <t>111294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>150179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255183</t>
+          <t>252760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45056</t>
+          <t>44456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71925</t>
+          <t>72379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>20922</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55977</t>
+          <t>55637</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69816</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117130</t>
+          <t>116706</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356990</t>
+          <t>355991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>392355</t>
+          <t>391788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>588265</t>
+          <t>584040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>688216</t>
+          <t>677302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>959217</t>
+          <t>960606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1053254</t>
+          <t>1056811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50281</t>
+          <t>52021</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80600</t>
+          <t>80610</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>99266</t>
+          <t>101060</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>161975</t>
+          <t>163734</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>163348</t>
+          <t>163097</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>229588</t>
+          <t>229672</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>26523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47742</t>
+          <t>47569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61552</t>
+          <t>61769</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99184</t>
+          <t>100004</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95183</t>
+          <t>96214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140013</t>
+          <t>138256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>232301</t>
+          <t>231374</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>238965</t>
+          <t>238932</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>499419</t>
+          <t>498164</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>542107</t>
+          <t>540850</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>733406</t>
+          <t>731105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>782037</t>
+          <t>781188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134211</t>
+          <t>135736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169368</t>
+          <t>168441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134654</t>
+          <t>136912</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>173838</t>
+          <t>174449</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76996</t>
+          <t>78240</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104143</t>
+          <t>105259</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77355</t>
+          <t>78625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>105938</t>
+          <t>107969</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2070319</t>
+          <t>2163241</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2895238</t>
+          <t>2897179</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2770056</t>
+          <t>2770798</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2977291</t>
+          <t>2976151</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4632268</t>
+          <t>4814825</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5742816</t>
+          <t>5740178</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,55%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>334596</t>
+          <t>334504</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1200130</t>
+          <t>1095984</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>383857</t>
+          <t>393475</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>525908</t>
+          <t>526395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>804470</t>
+          <t>802263</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1981681</t>
+          <t>1765727</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103504</t>
+          <t>103810</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>159867</t>
+          <t>160966</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>214852</t>
+          <t>212708</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>293499</t>
+          <t>291289</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>346176</t>
+          <t>342431</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>442207</t>
+          <t>436232</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0801-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>415208</t>
+          <t>415571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>441572</t>
+          <t>442250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>247563</t>
+          <t>247914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>272367</t>
+          <t>273050</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>672459</t>
+          <t>673539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>707924</t>
+          <t>708616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>45641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47580</t>
+          <t>48459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76788</t>
+          <t>78246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>16699</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40432</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336557</t>
+          <t>335982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355459</t>
+          <t>354940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339248</t>
+          <t>340575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358096</t>
+          <t>358087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683152</t>
+          <t>683868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>708214</t>
+          <t>708989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>24333</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>22107</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40072</t>
+          <t>40641</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>464158</t>
+          <t>463089</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>493283</t>
+          <t>492734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115830</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137448</t>
+          <t>137762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>585505</t>
+          <t>587521</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>624002</t>
+          <t>624038</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>34462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60683</t>
+          <t>60441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21562</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40454</t>
+          <t>40577</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60688</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93561</t>
+          <t>93651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>24597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39134</t>
+          <t>38283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1031359</t>
+          <t>1030315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1079190</t>
+          <t>1079265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>558533</t>
+          <t>560333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>601272</t>
+          <t>600041</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1608063</t>
+          <t>1604980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1670412</t>
+          <t>1668287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113197</t>
+          <t>112907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156501</t>
+          <t>156294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>90898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129505</t>
+          <t>127920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214133</t>
+          <t>214358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270967</t>
+          <t>275581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64145</t>
+          <t>61128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35460</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56959</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92205</t>
+          <t>88410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287826</t>
+          <t>287286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312980</t>
+          <t>312341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>436687</t>
+          <t>432998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>473954</t>
+          <t>472428</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>733011</t>
+          <t>727157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>778539</t>
+          <t>777211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>26714</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48951</t>
+          <t>49031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65047</t>
+          <t>65612</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99525</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98694</t>
+          <t>99096</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>138926</t>
+          <t>141793</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22360</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45011</t>
+          <t>46854</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>34045</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60497</t>
+          <t>61843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>283642</t>
+          <t>283870</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>294573</t>
+          <t>294490</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845228</t>
+          <t>847509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>911194</t>
+          <t>910717</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1135389</t>
+          <t>1136107</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1200675</t>
+          <t>1201079</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>245030</t>
+          <t>245846</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>301359</t>
+          <t>301968</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>249179</t>
+          <t>248134</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>308573</t>
+          <t>308554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77267</t>
+          <t>77319</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116352</t>
+          <t>116295</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79583</t>
+          <t>81508</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117823</t>
+          <t>119420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2867022</t>
+          <t>2868132</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2939619</t>
+          <t>2938795</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2605982</t>
+          <t>2604967</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2703442</t>
+          <t>2703412</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5495115</t>
+          <t>5500325</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5612627</t>
+          <t>5621038</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>236065</t>
+          <t>230193</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>298654</t>
+          <t>294612</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>499510</t>
+          <t>497902</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>585959</t>
+          <t>583629</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>755447</t>
+          <t>752576</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>862237</t>
+          <t>865332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82784</t>
+          <t>83461</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121848</t>
+          <t>122575</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>156687</t>
+          <t>156808</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>211582</t>
+          <t>212100</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>253517</t>
+          <t>253908</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>320932</t>
+          <t>319281</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>373026</t>
+          <t>372789</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>401011</t>
+          <t>401236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>262750</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288270</t>
+          <t>288095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>646284</t>
+          <t>644271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>683479</t>
+          <t>682918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55909</t>
+          <t>58400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43609</t>
+          <t>43356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54852</t>
+          <t>55188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89065</t>
+          <t>89179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350007</t>
+          <t>350421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>380315</t>
+          <t>380338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288345</t>
+          <t>288736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312879</t>
+          <t>312858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648436</t>
+          <t>648194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>687469</t>
+          <t>688102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26273</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>52354</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15590</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>36493</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47559</t>
+          <t>47544</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80327</t>
+          <t>79586</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>24179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>502496</t>
+          <t>499598</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>542006</t>
+          <t>542111</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178850</t>
+          <t>181316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>208262</t>
+          <t>208611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>691856</t>
+          <t>691860</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>740986</t>
+          <t>744330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55086</t>
+          <t>54064</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>89533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27750</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51803</t>
+          <t>52599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88529</t>
+          <t>88820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130085</t>
+          <t>131975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25601</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>52595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>36493</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80236</t>
+          <t>84501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>933790</t>
+          <t>933807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>986956</t>
+          <t>987582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624931</t>
+          <t>622192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>665582</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1573025</t>
+          <t>1569227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1639270</t>
+          <t>1638689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102226</t>
+          <t>102385</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147444</t>
+          <t>145943</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64728</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100642</t>
+          <t>99453</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178226</t>
+          <t>178212</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232154</t>
+          <t>234940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58430</t>
+          <t>58275</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94242</t>
+          <t>92283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29634</t>
+          <t>29188</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55324</t>
+          <t>54885</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>94859</t>
+          <t>96595</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137883</t>
+          <t>138375</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>402966</t>
+          <t>404624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>437379</t>
+          <t>439476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>478082</t>
+          <t>476871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>531143</t>
+          <t>530961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>894477</t>
+          <t>897159</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958061</t>
+          <t>961986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45549</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74689</t>
+          <t>74516</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135390</t>
+          <t>135993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>184074</t>
+          <t>182927</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>191139</t>
+          <t>190497</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>244821</t>
+          <t>246923</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>19863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40621</t>
+          <t>40903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79968</t>
+          <t>79571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117429</t>
+          <t>120004</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104521</t>
+          <t>107517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146980</t>
+          <t>148397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>248182</t>
+          <t>249246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>261969</t>
+          <t>261950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>695785</t>
+          <t>692235</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>760573</t>
+          <t>757243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>949666</t>
+          <t>949055</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1019039</t>
+          <t>1018656</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>216889</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>273426</t>
+          <t>274608</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>221468</t>
+          <t>222031</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278971</t>
+          <t>282893</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114566</t>
+          <t>115870</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>162091</t>
+          <t>161217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>119434</t>
+          <t>119455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>165593</t>
+          <t>166276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2874003</t>
+          <t>2876406</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2963717</t>
+          <t>2962409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2596738</t>
+          <t>2599191</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2703985</t>
+          <t>2704386</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5500427</t>
+          <t>5498306</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5635453</t>
+          <t>5639342</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>298127</t>
+          <t>301011</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>373716</t>
+          <t>372612</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>533256</t>
+          <t>532668</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>623652</t>
+          <t>622536</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>859238</t>
+          <t>853983</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>971515</t>
+          <t>968963</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>138505</t>
+          <t>137805</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>195358</t>
+          <t>192369</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>288322</t>
+          <t>284462</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>356813</t>
+          <t>353998</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>445581</t>
+          <t>441282</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>532866</t>
+          <t>533301</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>372798</t>
+          <t>371096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396854</t>
+          <t>398416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292225</t>
+          <t>291876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>317961</t>
+          <t>318194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>671823</t>
+          <t>671831</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>708762</t>
+          <t>708513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42957</t>
+          <t>42115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,49 +7713,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>24201</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15845</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34755</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>10,01%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24201</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15535</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>35231</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>49</t>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41007</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72599</t>
+          <t>71196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43219</t>
+          <t>45760</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325984</t>
+          <t>327258</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>350727</t>
+          <t>350938</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319953</t>
+          <t>319987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345481</t>
+          <t>345739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655227</t>
+          <t>654790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>690173</t>
+          <t>690451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>37427</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37386</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>35991</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>66871</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36131</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>429644</t>
+          <t>426240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>461603</t>
+          <t>460023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112551</t>
+          <t>113948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137641</t>
+          <t>138814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>550137</t>
+          <t>547739</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>591142</t>
+          <t>589043</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39604</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65059</t>
+          <t>64830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38170</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59493</t>
+          <t>62188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93489</t>
+          <t>98061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38835</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29310</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>939811</t>
+          <t>941433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>992074</t>
+          <t>992647</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>664980</t>
+          <t>665522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>709573</t>
+          <t>709395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1623191</t>
+          <t>1621903</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1690932</t>
+          <t>1689930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103322</t>
+          <t>102943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146902</t>
+          <t>148334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66019</t>
+          <t>66953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100698</t>
+          <t>102471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178672</t>
+          <t>180997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234305</t>
+          <t>235531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43008</t>
+          <t>42955</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72370</t>
+          <t>71764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40703</t>
+          <t>41111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71299</t>
+          <t>71592</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93177</t>
+          <t>91576</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>136458</t>
+          <t>133935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>474888</t>
+          <t>472548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>513569</t>
+          <t>512701</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>498778</t>
+          <t>501320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>552311</t>
+          <t>552468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>985493</t>
+          <t>986569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1050749</t>
+          <t>1051199</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73800</t>
+          <t>73943</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>108678</t>
+          <t>109107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>115526</t>
+          <t>116669</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160803</t>
+          <t>160285</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>203059</t>
+          <t>203614</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>258494</t>
+          <t>258481</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24077</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>47828</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57727</t>
+          <t>57690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91680</t>
+          <t>91489</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90169</t>
+          <t>88104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131512</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>273432</t>
+          <t>274403</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>284939</t>
+          <t>284973</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>720451</t>
+          <t>723468</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>788184</t>
+          <t>787808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1003622</t>
+          <t>1001268</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1067962</t>
+          <t>1071489</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>179106</t>
+          <t>176986</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>231329</t>
+          <t>232216</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180668</t>
+          <t>180320</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>236406</t>
+          <t>235568</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101271</t>
+          <t>103088</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146982</t>
+          <t>149411</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102792</t>
+          <t>105510</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>150354</t>
+          <t>153231</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2875965</t>
+          <t>2876294</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2956704</t>
+          <t>2953691</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2680991</t>
+          <t>2680889</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2784292</t>
+          <t>2789190</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5587370</t>
+          <t>5578221</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5716807</t>
+          <t>5712883</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>288433</t>
+          <t>293111</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>357201</t>
+          <t>361273</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>452566</t>
+          <t>455131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>542848</t>
+          <t>541639</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>767267</t>
+          <t>768443</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>878087</t>
+          <t>880150</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124154</t>
+          <t>123636</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>170794</t>
+          <t>169908</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>265470</t>
+          <t>264690</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>339286</t>
+          <t>337287</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>402373</t>
+          <t>404735</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>490282</t>
+          <t>489532</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>468527</t>
+          <t>509404</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>455050</t>
+          <t>497622</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>477503</t>
+          <t>520807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>394157</t>
+          <t>426187</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>382518</t>
+          <t>413935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>404816</t>
+          <t>437391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>862684</t>
+          <t>935591</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>846240</t>
+          <t>917207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>876877</t>
+          <t>950456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33439</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47945</t>
+          <t>55138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>61208</t>
+          <t>69055</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49602</t>
+          <t>56460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74345</t>
+          <t>83563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>18547</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22513</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>28787</t>
+          <t>34383</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>46444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399131</t>
+          <t>427459</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384320</t>
+          <t>412400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410851</t>
+          <t>441197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,17 +11497,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>327207</t>
+          <t>361905</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315447</t>
+          <t>350634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337778</t>
+          <t>374007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,27 +11532,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>726338</t>
+          <t>789363</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708618</t>
+          <t>769139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743160</t>
+          <t>806834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41862</t>
+          <t>43760</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>31961</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57055</t>
+          <t>57383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39195</t>
+          <t>42647</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30521</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49352</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,27 +11645,27 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>81057</t>
+          <t>86407</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>65656</t>
+          <t>70983</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>96675</t>
+          <t>104942</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -11688,17 +11688,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>19782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23479</t>
+          <t>26472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27398</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37981</t>
+          <t>42379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>352244</t>
+          <t>394689</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138935</t>
+          <t>378884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>562832</t>
+          <t>409210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120961</t>
+          <t>136683</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111481</t>
+          <t>126728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129436</t>
+          <t>146221</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>473205</t>
+          <t>531372</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218092</t>
+          <t>513277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>675972</t>
+          <t>547921</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>297618</t>
+          <t>58103</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>520218</t>
+          <t>72604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23125</t>
+          <t>25742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>327376</t>
+          <t>90729</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110501</t>
+          <t>75901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>600364</t>
+          <t>107853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18402</t>
+          <t>18820</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,17 +12179,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>12637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>25789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>37007</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54007</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>843702</t>
+          <t>923228</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>819811</t>
+          <t>898668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>868782</t>
+          <t>950140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>854210</t>
+          <t>723806</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>815638</t>
+          <t>705839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>908470</t>
+          <t>739022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1697911</t>
+          <t>1647034</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1651780</t>
+          <t>1614263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1798414</t>
+          <t>1676285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>84,11%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>134517</t>
+          <t>145163</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115350</t>
+          <t>121203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158101</t>
+          <t>166118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>93539</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>79924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111294</t>
+          <t>107213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>218134</t>
+          <t>238702</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150179</t>
+          <t>212864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252760</t>
+          <t>266472</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56600</t>
+          <t>63452</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>50512</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>80963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40267</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55637</t>
+          <t>55045</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>96867</t>
+          <t>107318</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>66054</t>
+          <t>91244</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116706</t>
+          <t>127175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>374860</t>
+          <t>460726</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355991</t>
+          <t>439838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>391788</t>
+          <t>477075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>621030</t>
+          <t>593250</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>584040</t>
+          <t>571998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>677302</t>
+          <t>612724</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>995890</t>
+          <t>1053976</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>960606</t>
+          <t>1024022</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1056811</t>
+          <t>1080982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>77,28%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64614</t>
+          <t>68797</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>55121</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80610</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>136430</t>
+          <t>143858</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>101060</t>
+          <t>128325</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>163734</t>
+          <t>160662</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>201044</t>
+          <t>212654</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>163097</t>
+          <t>190092</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>229672</t>
+          <t>235638</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35572</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26523</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47569</t>
+          <t>50928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>83875</t>
+          <t>93743</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61769</t>
+          <t>79818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100004</t>
+          <t>108400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>119447</t>
+          <t>132184</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96214</t>
+          <t>116378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138256</t>
+          <t>153809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>236632</t>
+          <t>233373</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231374</t>
+          <t>228598</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>238932</t>
+          <t>235739</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>519948</t>
+          <t>581962</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>498164</t>
+          <t>556440</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>540850</t>
+          <t>604077</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>756581</t>
+          <t>815335</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>731105</t>
+          <t>791390</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>781188</t>
+          <t>840587</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>150812</t>
+          <t>163379</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135736</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168441</t>
+          <t>182266</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>153594</t>
+          <t>166053</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136912</t>
+          <t>147929</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>174449</t>
+          <t>185119</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>90611</t>
+          <t>98940</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78240</t>
+          <t>84680</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105259</t>
+          <t>114721</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>91703</t>
+          <t>100121</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>78625</t>
+          <t>85372</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>116256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2675096</t>
+          <t>2948879</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2163241</t>
+          <t>2907509</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2897179</t>
+          <t>2988381</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2837514</t>
+          <t>2823792</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2770798</t>
+          <t>2781453</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2976151</t>
+          <t>2866000</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5512610</t>
+          <t>5772671</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4814825</t>
+          <t>5716640</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5740178</t>
+          <t>5831398</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>564428</t>
+          <t>343874</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>334504</t>
+          <t>310588</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1095984</t>
+          <t>378457</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>477985</t>
+          <t>519727</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>393475</t>
+          <t>486714</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>526395</t>
+          <t>557272</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1042413</t>
+          <t>863601</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>802263</t>
+          <t>818241</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1765727</t>
+          <t>910243</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>136536</t>
+          <t>149723</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103810</t>
+          <t>125962</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>160966</t>
+          <t>175063</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>262259</t>
+          <t>291874</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>212708</t>
+          <t>264801</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>291289</t>
+          <t>317889</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>398795</t>
+          <t>441597</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>342431</t>
+          <t>406538</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>436232</t>
+          <t>474355</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
